--- a/design/tables/Enemy.xlsx
+++ b/design/tables/Enemy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="Re9d71ef147ab4083"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="R25c1b42a55a7491e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -298,6 +298,9 @@
     <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
@@ -343,6 +346,15 @@
       <x:c r="N1" s="6" t="str">
         <x:v>显示比例</x:v>
       </x:c>
+      <x:c r="O1" s="6" t="str">
+        <x:v>挑战怪群精灵比例</x:v>
+      </x:c>
+      <x:c r="P1" s="6" t="str">
+        <x:v>挑战身体占位半径</x:v>
+      </x:c>
+      <x:c r="Q1" s="6" t="str">
+        <x:v>身体中心距脚底</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -385,6 +397,15 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="O2" s="3" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="P2" s="3" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="Q2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -431,6 +452,15 @@
       <x:c r="N3" s="3" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="O3" s="3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="P3" s="3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Q3" s="3" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -475,6 +505,15 @@
       <x:c r="N4" s="6" t="str">
         <x:v>显示比例</x:v>
       </x:c>
+      <x:c r="O4" s="6" t="str">
+        <x:v>crowdScale</x:v>
+      </x:c>
+      <x:c r="P4" s="6" t="str">
+        <x:v>crowdRadius</x:v>
+      </x:c>
+      <x:c r="Q4" s="6" t="str">
+        <x:v>crowdLift</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -519,6 +558,15 @@
       <x:c r="N5" s="5" t="str">
         <x:v>spriteScale</x:v>
       </x:c>
+      <x:c r="O5" s="5" t="str">
+        <x:v>crowdScale</x:v>
+      </x:c>
+      <x:c r="P5" s="5" t="str">
+        <x:v>crowdRadius</x:v>
+      </x:c>
+      <x:c r="Q5" s="5" t="str">
+        <x:v>crowdLift</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -560,6 +608,15 @@
       </x:c>
       <x:c r="N6" s="8" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="O6" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P6" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q6" s="8" t="n">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -603,6 +660,15 @@
       <x:c r="N7" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="O7" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P7" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q7" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="n">
@@ -645,6 +711,15 @@
       <x:c r="N8" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="O8" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P8" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q8" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="n">
@@ -687,6 +762,15 @@
       <x:c r="N9" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="O9" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P9" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q9" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="n">
@@ -729,6 +813,15 @@
       <x:c r="N10" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="O10" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P10" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q10" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="n">
@@ -771,6 +864,15 @@
       <x:c r="N11" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="O11" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P11" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q11" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="n">
@@ -815,6 +917,15 @@
       <x:c r="N12" s="8" t="n">
         <x:v>1.5</x:v>
       </x:c>
+      <x:c r="O12" s="8" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="P12" s="8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q12" s="8" t="n">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="7" t="n">
@@ -859,6 +970,15 @@
       <x:c r="N13" s="8" t="n">
         <x:v>1.5</x:v>
       </x:c>
+      <x:c r="O13" s="8" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="P13" s="8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q13" s="8" t="n">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="7" t="n">
@@ -903,6 +1023,15 @@
       <x:c r="N14" s="8" t="n">
         <x:v>1.5</x:v>
       </x:c>
+      <x:c r="O14" s="8" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="P14" s="8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q14" s="8" t="n">
+        <x:v>20.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="n">
@@ -946,6 +1075,15 @@
       </x:c>
       <x:c r="N15" s="8" t="n">
         <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="O15" s="8" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="P15" s="8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q15" s="8" t="n">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Enemy.xlsx
+++ b/design/tables/Enemy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="R25c1b42a55a7491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="Rf497e75434944fe5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1086,6 +1086,720 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="str">
+        <x:v>puff</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G16" s="2" t="str">
+        <x:v>#9a77bd</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="2" t="str">
+        <x:v>enemy.puff.name</x:v>
+      </x:c>
+      <x:c r="J16" s="2" t="str"/>
+      <x:c r="K16" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L16" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="7" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="N16" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O16" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P16" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q16" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="str">
+        <x:v>pudding</x:v>
+      </x:c>
+      <x:c r="C17" s="7" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F17" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G17" s="2" t="str">
+        <x:v>#9a77bd</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="2" t="str">
+        <x:v>enemy.pudding.name</x:v>
+      </x:c>
+      <x:c r="J17" s="2" t="str"/>
+      <x:c r="K17" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L17" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="7" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="N17" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O17" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P17" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q17" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="str">
+        <x:v>biscuit</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F18" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G18" s="2" t="str">
+        <x:v>#9a77bd</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="2" t="str">
+        <x:v>enemy.biscuit.name</x:v>
+      </x:c>
+      <x:c r="J18" s="2" t="str"/>
+      <x:c r="K18" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L18" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="7" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="N18" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O18" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P18" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q18" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" s="2" t="str">
+        <x:v>soda</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F19" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G19" s="2" t="str">
+        <x:v>#e5aa54</x:v>
+      </x:c>
+      <x:c r="H19" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I19" s="2" t="str">
+        <x:v>enemy.soda.name</x:v>
+      </x:c>
+      <x:c r="J19" s="2" t="str"/>
+      <x:c r="K19" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L19" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="7" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="N19" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O19" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P19" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q19" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="str">
+        <x:v>coffee</x:v>
+      </x:c>
+      <x:c r="C20" s="7" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F20" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G20" s="2" t="str">
+        <x:v>#e5aa54</x:v>
+      </x:c>
+      <x:c r="H20" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I20" s="2" t="str">
+        <x:v>enemy.coffee.name</x:v>
+      </x:c>
+      <x:c r="J20" s="2" t="str"/>
+      <x:c r="K20" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L20" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="7" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="N20" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O20" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P20" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q20" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" s="2" t="str">
+        <x:v>tea</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F21" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G21" s="2" t="str">
+        <x:v>#82a9d7</x:v>
+      </x:c>
+      <x:c r="H21" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" s="2" t="str">
+        <x:v>enemy.tea.name</x:v>
+      </x:c>
+      <x:c r="J21" s="2" t="str"/>
+      <x:c r="K21" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L21" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="7" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="N21" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O21" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P21" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q21" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B22" s="2" t="str">
+        <x:v>berrymilk</x:v>
+      </x:c>
+      <x:c r="C22" s="7" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F22" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G22" s="2" t="str">
+        <x:v>#82a9d7</x:v>
+      </x:c>
+      <x:c r="H22" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" s="2" t="str">
+        <x:v>enemy.berrymilk.name</x:v>
+      </x:c>
+      <x:c r="J22" s="2" t="str"/>
+      <x:c r="K22" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L22" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="7" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="N22" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O22" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P22" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q22" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B23" s="2" t="str">
+        <x:v>tin</x:v>
+      </x:c>
+      <x:c r="C23" s="7" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F23" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G23" s="2" t="str">
+        <x:v>#8fa9a4</x:v>
+      </x:c>
+      <x:c r="H23" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I23" s="2" t="str">
+        <x:v>enemy.tin.name</x:v>
+      </x:c>
+      <x:c r="J23" s="2" t="str"/>
+      <x:c r="K23" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L23" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23" s="7" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N23" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O23" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P23" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q23" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B24" s="2" t="str">
+        <x:v>juice</x:v>
+      </x:c>
+      <x:c r="C24" s="7" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F24" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G24" s="2" t="str">
+        <x:v>#8fa9a4</x:v>
+      </x:c>
+      <x:c r="H24" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I24" s="2" t="str">
+        <x:v>enemy.juice.name</x:v>
+      </x:c>
+      <x:c r="J24" s="2" t="str"/>
+      <x:c r="K24" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L24" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M24" s="7" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N24" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O24" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P24" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q24" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B25" s="2" t="str">
+        <x:v>peach</x:v>
+      </x:c>
+      <x:c r="C25" s="7" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F25" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G25" s="2" t="str">
+        <x:v>#87b873</x:v>
+      </x:c>
+      <x:c r="H25" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I25" s="2" t="str">
+        <x:v>enemy.peach.name</x:v>
+      </x:c>
+      <x:c r="J25" s="2" t="str"/>
+      <x:c r="K25" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L25" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M25" s="7" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="N25" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O25" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P25" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q25" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" s="2" t="str">
+        <x:v>grape</x:v>
+      </x:c>
+      <x:c r="C26" s="7" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F26" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G26" s="2" t="str">
+        <x:v>#87b873</x:v>
+      </x:c>
+      <x:c r="H26" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" s="2" t="str">
+        <x:v>enemy.grape.name</x:v>
+      </x:c>
+      <x:c r="J26" s="2" t="str"/>
+      <x:c r="K26" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L26" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="7" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="N26" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O26" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P26" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q26" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" s="2" t="str">
+        <x:v>blue</x:v>
+      </x:c>
+      <x:c r="C27" s="7" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F27" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G27" s="2" t="str">
+        <x:v>#87b873</x:v>
+      </x:c>
+      <x:c r="H27" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I27" s="2" t="str">
+        <x:v>enemy.blue.name</x:v>
+      </x:c>
+      <x:c r="J27" s="2" t="str"/>
+      <x:c r="K27" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L27" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="7" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="N27" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O27" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P27" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q27" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" s="2" t="str">
+        <x:v>ricebox</x:v>
+      </x:c>
+      <x:c r="C28" s="7" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F28" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G28" s="2" t="str">
+        <x:v>#8a705c</x:v>
+      </x:c>
+      <x:c r="H28" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I28" s="2" t="str">
+        <x:v>enemy.ricebox.name</x:v>
+      </x:c>
+      <x:c r="J28" s="2" t="str"/>
+      <x:c r="K28" s="8" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="L28" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="7" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N28" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O28" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P28" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q28" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="str">
+        <x:v>deliverybag</x:v>
+      </x:c>
+      <x:c r="C29" s="7" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F29" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G29" s="2" t="str">
+        <x:v>#8a705c</x:v>
+      </x:c>
+      <x:c r="H29" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I29" s="2" t="str">
+        <x:v>enemy.deliverybag.name</x:v>
+      </x:c>
+      <x:c r="J29" s="2" t="str"/>
+      <x:c r="K29" s="8" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="L29" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="7" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N29" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O29" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P29" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q29" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/Enemy.xlsx
+++ b/design/tables/Enemy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="Rf497e75434944fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="Rf205c1a908e7497a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1800,6 +1800,316 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" s="2" t="str">
+        <x:v>mochi</x:v>
+      </x:c>
+      <x:c r="C30" s="7" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F30" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G30" s="2" t="str">
+        <x:v>#87b873</x:v>
+      </x:c>
+      <x:c r="H30" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" s="2" t="str">
+        <x:v>enemy.mochi.name</x:v>
+      </x:c>
+      <x:c r="J30" s="2" t="str"/>
+      <x:c r="K30" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L30" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M30" s="7" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="N30" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O30" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P30" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q30" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" s="2" t="str">
+        <x:v>popcorn</x:v>
+      </x:c>
+      <x:c r="C31" s="7" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F31" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G31" s="2" t="str">
+        <x:v>#e5aa54</x:v>
+      </x:c>
+      <x:c r="H31" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" s="2" t="str">
+        <x:v>enemy.popcorn.name</x:v>
+      </x:c>
+      <x:c r="J31" s="2" t="str"/>
+      <x:c r="K31" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L31" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M31" s="7" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="N31" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O31" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P31" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q31" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" s="2" t="str">
+        <x:v>noodlecup</x:v>
+      </x:c>
+      <x:c r="C32" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G32" s="2" t="str">
+        <x:v>#8a705c</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I32" s="2" t="str">
+        <x:v>enemy.noodlecup.name</x:v>
+      </x:c>
+      <x:c r="J32" s="2" t="str"/>
+      <x:c r="K32" s="8" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="L32" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M32" s="7" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N32" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O32" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P32" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q32" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" s="2" t="str">
+        <x:v>frostdonut</x:v>
+      </x:c>
+      <x:c r="C33" s="7" t="n">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G33" s="2" t="str">
+        <x:v>#8fa9a4</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I33" s="2" t="str">
+        <x:v>enemy.frostdonut.name</x:v>
+      </x:c>
+      <x:c r="J33" s="2" t="str"/>
+      <x:c r="K33" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L33" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M33" s="7" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N33" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O33" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P33" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q33" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" s="2" t="str">
+        <x:v>freezer</x:v>
+      </x:c>
+      <x:c r="C34" s="7" t="n">
+        <x:v>2100</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G34" s="2" t="str">
+        <x:v>#ca845b</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I34" s="2" t="str">
+        <x:v>enemy.freezer.name</x:v>
+      </x:c>
+      <x:c r="J34" s="2" t="str">
+        <x:v>mini</x:v>
+      </x:c>
+      <x:c r="K34" s="8" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="L34" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="7" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="N34" s="8" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="O34" s="8" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="P34" s="8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q34" s="8" t="n">
+        <x:v>20.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" s="2" t="str">
+        <x:v>vending</x:v>
+      </x:c>
+      <x:c r="C35" s="7" t="n">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F35" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G35" s="2" t="str">
+        <x:v>#877494</x:v>
+      </x:c>
+      <x:c r="H35" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I35" s="2" t="str">
+        <x:v>enemy.vending.name</x:v>
+      </x:c>
+      <x:c r="J35" s="2" t="str">
+        <x:v>major</x:v>
+      </x:c>
+      <x:c r="K35" s="8" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="L35" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="7" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="N35" s="8" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="O35" s="8" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="P35" s="8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q35" s="8" t="n">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
